--- a/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_64974_completo.xlsx
+++ b/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_64974_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2e2a96dc5aa744d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R45befb4db2b843f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    278.3419</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    272.7704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    274.7878</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    276.2003</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.0888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.0877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.8974</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.1889</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    274.4814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_64974_completo.xlsx
+++ b/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_64974_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R45befb4db2b843f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2d9d942f3c3644af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,651 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    265.1777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    268.1784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    270.4630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    257.2665</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    262.0533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    288.9096</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    346.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    266.8481</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.5149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    268.6922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    263.9935</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    292.8790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    330.6404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    291.0176</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    291.1278</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    308.8896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    299.4678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    330.1065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    389.9995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    483.1387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    341.8809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.3345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    270.4734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    273.5095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    276.2104</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    284.9729</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.2582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    279.7749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    287.5671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.0451</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    277.4586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    271.6609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    276.6119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    278.4405</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    279.8741</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    280.7914</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    277.8296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    276.3080</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    326.4754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    411.6262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    301.2470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    270.5683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.5599</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
